--- a/data/trans_dic/IP2001-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen caries</t>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,44</t>
+          <t>0,0; 11,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 5,88</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,0</t>
+          <t>2,88; 6,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 12,2</t>
+          <t>5,77; 11,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 12,36</t>
+          <t>5,78; 12,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,2</t>
+          <t>1,81; 6,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,73</t>
+          <t>2,58; 6,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 9,82</t>
+          <t>4,05; 9,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 10,03</t>
+          <t>4,72; 10,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,38</t>
+          <t>2,96; 8,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,99</t>
+          <t>3,23; 6,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,41</t>
+          <t>5,49; 9,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,88</t>
+          <t>5,84; 10,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,68</t>
+          <t>2,94; 6,65</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 19,53</t>
+          <t>9,8; 19,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,22; 20,52</t>
+          <t>10,59; 20,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,07; 21,03</t>
+          <t>11,68; 20,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 10,18</t>
+          <t>3,64; 10,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 18,5</t>
+          <t>9,37; 18,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,91; 18,06</t>
+          <t>8,99; 18,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,8; 22,07</t>
+          <t>13,13; 22,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 10,17</t>
+          <t>3,83; 10,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,76; 17,36</t>
+          <t>10,5; 17,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,98; 17,79</t>
+          <t>11,04; 18,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,33; 19,54</t>
+          <t>13,52; 19,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,96</t>
+          <t>4,47; 9,05</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,59; 17,63</t>
+          <t>9,75; 17,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 15,06</t>
+          <t>7,06; 15,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 16,8</t>
+          <t>8,76; 17,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,88</t>
+          <t>2,08; 5,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 16,03</t>
+          <t>8,51; 15,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 20,8</t>
+          <t>11,7; 20,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,64</t>
+          <t>6,59; 14,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,37</t>
+          <t>4,39; 10,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 15,9</t>
+          <t>9,85; 15,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 16,24</t>
+          <t>10,62; 16,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 14,24</t>
+          <t>8,66; 14,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,53</t>
+          <t>3,93; 7,52</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,33</t>
+          <t>6,72; 10,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,02</t>
+          <t>7,74; 11,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,58</t>
+          <t>8,71; 12,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,78</t>
+          <t>3,14; 5,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,72</t>
+          <t>6,46; 9,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,4</t>
+          <t>7,65; 11,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,71</t>
+          <t>7,95; 11,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,86</t>
+          <t>4,47; 7,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,44</t>
+          <t>7,1; 9,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 10,79</t>
+          <t>8,03; 10,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,57</t>
+          <t>8,85; 11,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,48</t>
+          <t>4,19; 6,39</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen caries (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5575</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2843</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2866</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5664</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11306</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19958</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17989</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5509</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11115</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17360</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18112</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9616</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>22421</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37318</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>36101</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>15126</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7232; 17187</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13588; 27928</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12122; 25761</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2857; 10224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6462; 17220</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10855; 25038</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12150; 26247</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>5379; 16011</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>16194; 30732</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>27647; 48268</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>27307; 46865</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9963; 22534</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>17641</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23420</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29773</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10807</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19053</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20775</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31910</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>13939</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>36695</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>44195</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>61683</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>24746</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12449; 24877</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16521; 31997</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21949; 38593</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6308; 17494</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13118; 25895</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14251; 29110</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24669; 41945</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8139; 22514</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>28053; 45819</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>34710; 56834</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>50820; 73912</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>17246; 34894</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>25230</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18117</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21419</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10501</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23919</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27823</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17374</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>21203</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>49149</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>45940</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>38793</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>31703</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>18804; 33608</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11916; 25554</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15176; 30402</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5734; 16329</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17144; 31435</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>20842; 36993</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>11476; 24612</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>13358; 31853</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>38836; 60309</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>36849; 56403</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>30082; 49595</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>22800; 43590</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>54177</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>61495</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>69182</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28454</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>44758</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>108265</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>127453</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>137136</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>73212</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>43146; 66270</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51020; 77399</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>57365; 83173</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20541; 38987</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>43736; 67227</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>53595; 80425</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>55615; 82868</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>33339; 57334</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>93664; 124699</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>109273; 147774</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>120256; 155821</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>58646; 89442</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2001-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Edad-trans_dic.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,52</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,88</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,84</t>
+          <t>2,76; 7,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 11,86</t>
+          <t>5,7; 11,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 12,28</t>
+          <t>5,82; 12,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,49</t>
+          <t>1,54; 6,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,87</t>
+          <t>2,66; 6,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,33</t>
+          <t>4,13; 9,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 10,2</t>
+          <t>4,65; 9,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,82</t>
+          <t>2,88; 8,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,12</t>
+          <t>3,19; 6,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 9,58</t>
+          <t>5,56; 9,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,03</t>
+          <t>5,85; 10,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,65</t>
+          <t>3,05; 6,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 19,59</t>
+          <t>10,01; 19,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,59; 20,52</t>
+          <t>10,85; 19,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,68; 20,54</t>
+          <t>11,74; 20,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,11</t>
+          <t>3,59; 9,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,37; 18,49</t>
+          <t>9,97; 18,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 18,36</t>
+          <t>9,39; 18,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,13; 22,32</t>
+          <t>12,64; 21,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 10,6</t>
+          <t>3,93; 10,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 17,16</t>
+          <t>10,26; 17,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,04; 18,07</t>
+          <t>11,24; 17,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 19,67</t>
+          <t>13,42; 19,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 9,05</t>
+          <t>4,36; 8,96</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 17,43</t>
+          <t>9,93; 17,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 15,13</t>
+          <t>7,33; 14,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 17,54</t>
+          <t>8,79; 17,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,93</t>
+          <t>2,08; 6,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,6</t>
+          <t>8,41; 16,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 20,77</t>
+          <t>12,03; 20,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,14</t>
+          <t>6,62; 14,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,48</t>
+          <t>4,56; 10,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 15,29</t>
+          <t>9,89; 15,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 16,26</t>
+          <t>10,48; 16,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,28</t>
+          <t>8,56; 14,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,52</t>
+          <t>3,88; 7,66</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,32</t>
+          <t>6,78; 10,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,74</t>
+          <t>7,47; 11,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,62</t>
+          <t>8,7; 12,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 5,96</t>
+          <t>3,09; 5,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 9,92</t>
+          <t>6,4; 9,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,48</t>
+          <t>7,85; 11,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,84</t>
+          <t>7,93; 11,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,69</t>
+          <t>4,39; 7,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 9,45</t>
+          <t>7,03; 9,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,87</t>
+          <t>8,25; 10,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,47</t>
+          <t>8,8; 11,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,39</t>
+          <t>4,22; 6,41</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5575</t>
+          <t>0; 5475</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2843</t>
+          <t>0; 3151</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2866</t>
+          <t>0; 2798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5664</t>
+          <t>0; 6057</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7232; 17187</t>
+          <t>6942; 18193</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13588; 27928</t>
+          <t>13426; 28122</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12122; 25761</t>
+          <t>12206; 25776</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2857; 10224</t>
+          <t>2420; 9846</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6462; 17220</t>
+          <t>6680; 17060</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10855; 25038</t>
+          <t>11081; 25824</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12150; 26247</t>
+          <t>11960; 25610</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5379; 16011</t>
+          <t>5233; 16159</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16194; 30732</t>
+          <t>16011; 30529</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27647; 48268</t>
+          <t>28026; 47812</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27307; 46865</t>
+          <t>27350; 46862</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9963; 22534</t>
+          <t>10348; 23691</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12449; 24877</t>
+          <t>12719; 25194</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16521; 31997</t>
+          <t>16919; 30868</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21949; 38593</t>
+          <t>22054; 37844</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6308; 17494</t>
+          <t>6214; 17009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13118; 25895</t>
+          <t>13965; 26420</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14251; 29110</t>
+          <t>14883; 29044</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24669; 41945</t>
+          <t>23763; 40133</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8139; 22514</t>
+          <t>8357; 23025</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28053; 45819</t>
+          <t>27399; 45645</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34710; 56834</t>
+          <t>35356; 56457</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50820; 73912</t>
+          <t>50425; 74400</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17246; 34894</t>
+          <t>16814; 34558</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18804; 33608</t>
+          <t>19144; 34519</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11916; 25554</t>
+          <t>12377; 25085</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15176; 30402</t>
+          <t>15241; 29987</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5734; 16329</t>
+          <t>5721; 16698</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17144; 31435</t>
+          <t>16949; 32493</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20842; 36993</t>
+          <t>21421; 35645</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11476; 24612</t>
+          <t>11517; 24821</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13358; 31853</t>
+          <t>13848; 31284</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38836; 60309</t>
+          <t>38985; 60121</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36849; 56403</t>
+          <t>36377; 57396</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30082; 49595</t>
+          <t>29733; 49736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22800; 43590</t>
+          <t>22466; 44391</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43146; 66270</t>
+          <t>43502; 66367</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51020; 77399</t>
+          <t>49264; 74585</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57365; 83173</t>
+          <t>57351; 81317</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20541; 38987</t>
+          <t>20251; 38001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43736; 67227</t>
+          <t>43372; 66992</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53595; 80425</t>
+          <t>54990; 81579</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55615; 82868</t>
+          <t>55501; 82084</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33339; 57334</t>
+          <t>32717; 57977</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93664; 124699</t>
+          <t>92812; 124278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109273; 147774</t>
+          <t>112165; 147484</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120256; 155821</t>
+          <t>119580; 153733</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58646; 89442</t>
+          <t>59127; 89761</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2001-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP2001-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -659,14 +659,14 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -679,24 +679,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -727,14 +727,14 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,58</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,31</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 11,45</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 5,85</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,5%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,47%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>8,57%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,24</t>
+          <t>2,59; 6,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,94</t>
+          <t>4,23; 9,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 12,28</t>
+          <t>4,47; 10,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,25</t>
+          <t>3,18; 9,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,8</t>
+          <t>2,77; 7,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 9,63</t>
+          <t>5,74; 12,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,95</t>
+          <t>5,95; 12,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,9</t>
+          <t>1,54; 6,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,08</t>
+          <t>3,13; 5,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,56; 9,49</t>
+          <t>5,65; 9,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,03</t>
+          <t>5,93; 9,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,99</t>
+          <t>2,99; 7,01</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13,89%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>15,02%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>15,85%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 19,84</t>
+          <t>8,89; 18,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,85; 19,79</t>
+          <t>8,91; 18,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,74; 20,14</t>
+          <t>12,8; 22,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,83</t>
+          <t>3,9; 10,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,97; 18,86</t>
+          <t>9,67; 19,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 18,32</t>
+          <t>11,22; 20,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,64; 21,36</t>
+          <t>12,07; 21,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,84</t>
+          <t>3,67; 10,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 17,09</t>
+          <t>10,76; 17,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,24; 17,95</t>
+          <t>10,98; 17,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 19,8</t>
+          <t>13,33; 19,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,96</t>
+          <t>4,55; 9,25</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,73%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12,36%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 17,9</t>
+          <t>8,39; 16,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 14,86</t>
+          <t>11,7; 20,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 17,3</t>
+          <t>6,81; 14,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,06</t>
+          <t>4,46; 10,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 16,12</t>
+          <t>9,59; 17,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,03; 20,01</t>
+          <t>7,12; 15,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 14,26</t>
+          <t>8,35; 16,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,29</t>
+          <t>2,48; 6,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 15,24</t>
+          <t>9,98; 15,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,48; 16,54</t>
+          <t>10,51; 16,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 14,32</t>
+          <t>8,31; 14,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,66</t>
+          <t>4,14; 7,89</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,44%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,34</t>
+          <t>6,51; 9,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,31</t>
+          <t>7,68; 11,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,34</t>
+          <t>7,9; 11,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,81</t>
+          <t>4,65; 8,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,89</t>
+          <t>6,75; 10,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,64</t>
+          <t>7,43; 11,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,73</t>
+          <t>8,53; 12,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,77</t>
+          <t>3,31; 6,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 9,42</t>
+          <t>7,11; 9,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 10,84</t>
+          <t>8,13; 10,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 11,32</t>
+          <t>8,8; 11,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,41</t>
+          <t>4,42; 6,71</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1519,32 +1519,32 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1607,32 +1607,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>558</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1480</t>
         </is>
       </c>
     </row>
@@ -1655,14 +1655,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 2874</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5475</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1675,32 +1675,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3151</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0; 5103</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2798</t>
+          <t>0; 2819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 6057</t>
+          <t>0; 4930</t>
         </is>
       </c>
     </row>
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11115</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17360</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18112</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8760</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11306</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19958</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>17989</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5509</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11115</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17360</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18112</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>13845</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6942; 18193</t>
+          <t>6488; 16874</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13426; 28122</t>
+          <t>11347; 26331</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12206; 25776</t>
+          <t>11512; 25814</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2420; 9846</t>
+          <t>4981; 15421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6680; 17060</t>
+          <t>6954; 17577</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11081; 25824</t>
+          <t>13512; 28743</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11960; 25610</t>
+          <t>12481; 25926</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5233; 16159</t>
+          <t>2208; 9061</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16011; 30529</t>
+          <t>15732; 30098</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28026; 47812</t>
+          <t>28471; 47391</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27350; 46862</t>
+          <t>27689; 46183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10348; 23691</t>
+          <t>8981; 21044</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>19053</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20775</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31910</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13689</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>17641</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>23420</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>29773</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10807</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>19053</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20775</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>31910</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24746</t>
+          <t>24674</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12719; 25194</t>
+          <t>12452; 25907</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16919; 30868</t>
+          <t>14121; 28633</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22054; 37844</t>
+          <t>24052; 41474</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6214; 17009</t>
+          <t>7803; 21196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13965; 26420</t>
+          <t>12279; 24811</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14883; 29044</t>
+          <t>17491; 32001</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23763; 40133</t>
+          <t>22680; 39514</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8357; 23025</t>
+          <t>6410; 17780</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27399; 45645</t>
+          <t>28726; 46360</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35356; 56457</t>
+          <t>34546; 55961</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50425; 74400</t>
+          <t>50077; 73425</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16814; 34558</t>
+          <t>17039; 34684</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23919</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27823</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17374</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20052</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>25230</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>18117</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>21419</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23919</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27823</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17374</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31703</t>
+          <t>31028</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19144; 34519</t>
+          <t>16916; 32305</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12377; 25085</t>
+          <t>20841; 37057</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15241; 29987</t>
+          <t>11850; 25489</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5721; 16698</t>
+          <t>12987; 29691</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16949; 32493</t>
+          <t>18500; 33989</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21421; 35645</t>
+          <t>12027; 25421</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11517; 24821</t>
+          <t>14478; 29108</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13848; 31284</t>
+          <t>6366; 16976</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38985; 60121</t>
+          <t>39366; 62686</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36377; 57396</t>
+          <t>36455; 56363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29733; 49736</t>
+          <t>28862; 49454</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22466; 44391</t>
+          <t>22684; 43197</t>
         </is>
       </c>
     </row>
@@ -2346,37 +2346,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>65958</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67954</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>54177</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>61495</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>69182</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28454</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>54087</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65958</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67954</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73212</t>
+          <t>71027</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43502; 66367</t>
+          <t>44124; 65847</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49264; 74585</t>
+          <t>53823; 79914</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57351; 81317</t>
+          <t>55272; 81936</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20251; 38001</t>
+          <t>31994; 56115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43372; 66992</t>
+          <t>43339; 66323</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54990; 81579</t>
+          <t>48968; 72618</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55501; 82084</t>
+          <t>56179; 82855</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32717; 57977</t>
+          <t>20523; 37760</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92812; 124278</t>
+          <t>93753; 124607</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>112165; 147484</t>
+          <t>110538; 146710</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119580; 153733</t>
+          <t>119570; 157149</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59127; 89761</t>
+          <t>57801; 87760</t>
         </is>
       </c>
     </row>
